--- a/demoplay/src/test/resources/ExcelValidation.xlsx
+++ b/demoplay/src/test/resources/ExcelValidation.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80632" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283398" uniqueCount="254">
   <si>
     <t>PayFree</t>
   </si>
@@ -11603,6 +11603,12 @@
   </si>
   <si>
     <t xml:space="preserve"> VOLO HEALTH INSURANCE TPA PVT LTD </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CORPORATECREDIT </t>
+  </si>
+  <si>
+    <t>Employee Grade</t>
   </si>
 </sst>
 </file>
@@ -12290,57 +12296,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:CNI16"/>
+  <dimension ref="A1:CNI17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="21.48046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="5.75" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.55078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="25.2890625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="19.76171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="12.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="24.38671875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="36.2421875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="18.98046875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.7265625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="19.84375" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.26953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="40.36328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="22.55078125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="19.8671875" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="17.25" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="19.72265625" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="13.9609375" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="23.515625" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="15.5546875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="39.6484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="32.5625" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="25.5546875" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="38.59765625" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="27.515625" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="16.3046875" customWidth="true" bestFit="true"/>
     <col min="20" max="20" width="18.078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.52734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.75" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.77734375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.61328125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="20.328125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="16.9140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="18.63671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="16.8359375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="15.92578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.6484375" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="20.9375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="25.76953125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="30.28515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.61328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="24.4453125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="21.58984375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="30.8203125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="31.34765625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.25390625" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.4765625" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="14.96484375" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="47.31640625" customWidth="true" bestFit="true"/>
     <col min="34" max="34" width="15.98046875" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="23.7265625" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="20.15234375" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="47.82421875" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="36.296875" customWidth="true" bestFit="true"/>
     <col min="37" max="37" width="27.08203125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="15.32421875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="15.09375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="14.25" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="29.95703125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="18.73046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="22.1484375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.36328125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="16.5078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="34.5390625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="29.84765625" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="24.859375" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="25.87890625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.765625" customWidth="true" bestFit="true"/>
     <col min="45" max="45" width="17.2109375" customWidth="true" bestFit="true"/>
     <col min="46" max="46" width="13.59375" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="18.76953125" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="17.87890625" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" width="41.92578125" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" width="41.60546875" customWidth="true" bestFit="true"/>
     <col min="49" max="49" width="30.3984375" customWidth="true" bestFit="true"/>
     <col min="50" max="50" width="15.421875" customWidth="true" bestFit="true"/>
   </cols>
@@ -22343,12 +22349,9 @@
         <v>3323</v>
       </c>
       <c r="AZ10" t="s" s="0">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="BA10" t="s" s="0">
-        <v>3325</v>
-      </c>
-      <c r="BB10" t="s" s="0">
         <v>3326</v>
       </c>
     </row>
@@ -23520,6 +23523,476 @@
       </c>
       <c r="CU16" t="s" s="0">
         <v>3706</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>3707</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>3708</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>3709</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>3710</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>3711</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>3712</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>3713</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>3714</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>3715</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>3716</v>
+      </c>
+      <c r="K17" t="s" s="0">
+        <v>3717</v>
+      </c>
+      <c r="L17" t="s" s="0">
+        <v>3718</v>
+      </c>
+      <c r="M17" t="s" s="0">
+        <v>3719</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>3720</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>3721</v>
+      </c>
+      <c r="P17" t="s" s="0">
+        <v>3722</v>
+      </c>
+      <c r="Q17" t="s" s="0">
+        <v>3723</v>
+      </c>
+      <c r="R17" t="s" s="0">
+        <v>3724</v>
+      </c>
+      <c r="S17" t="s" s="0">
+        <v>3725</v>
+      </c>
+      <c r="T17" t="s" s="0">
+        <v>3726</v>
+      </c>
+      <c r="U17" t="s" s="0">
+        <v>3727</v>
+      </c>
+      <c r="V17" t="s" s="0">
+        <v>3728</v>
+      </c>
+      <c r="W17" t="s" s="0">
+        <v>3729</v>
+      </c>
+      <c r="X17" t="s" s="0">
+        <v>3730</v>
+      </c>
+      <c r="Y17" t="s" s="0">
+        <v>3731</v>
+      </c>
+      <c r="Z17" t="s" s="0">
+        <v>3732</v>
+      </c>
+      <c r="AA17" t="s" s="0">
+        <v>3733</v>
+      </c>
+      <c r="AB17" t="s" s="0">
+        <v>3734</v>
+      </c>
+      <c r="AC17" t="s" s="0">
+        <v>3735</v>
+      </c>
+      <c r="AD17" t="s" s="0">
+        <v>3736</v>
+      </c>
+      <c r="AE17" t="s" s="0">
+        <v>3598</v>
+      </c>
+      <c r="AF17" t="s" s="0">
+        <v>3606</v>
+      </c>
+      <c r="AG17" t="s" s="0">
+        <v>3737</v>
+      </c>
+      <c r="AH17" t="s" s="0">
+        <v>3738</v>
+      </c>
+      <c r="AI17" t="s" s="0">
+        <v>3739</v>
+      </c>
+      <c r="AJ17" t="s" s="0">
+        <v>3740</v>
+      </c>
+      <c r="AK17" t="s" s="0">
+        <v>3741</v>
+      </c>
+      <c r="AL17" t="s" s="0">
+        <v>3742</v>
+      </c>
+      <c r="AM17" t="s" s="0">
+        <v>3743</v>
+      </c>
+      <c r="AN17" t="s" s="0">
+        <v>3744</v>
+      </c>
+      <c r="AO17" t="s" s="0">
+        <v>3745</v>
+      </c>
+      <c r="AP17" t="s" s="0">
+        <v>3746</v>
+      </c>
+      <c r="AQ17" t="s" s="0">
+        <v>3747</v>
+      </c>
+      <c r="AR17" t="s" s="0">
+        <v>3748</v>
+      </c>
+      <c r="AS17" t="s" s="0">
+        <v>3749</v>
+      </c>
+      <c r="AT17" t="s" s="0">
+        <v>3750</v>
+      </c>
+      <c r="AU17" t="s" s="0">
+        <v>3751</v>
+      </c>
+      <c r="AV17" t="s" s="0">
+        <v>3752</v>
+      </c>
+      <c r="AW17" t="s" s="0">
+        <v>3753</v>
+      </c>
+      <c r="AX17" t="s" s="0">
+        <v>3754</v>
+      </c>
+      <c r="AY17" t="s" s="0">
+        <v>3755</v>
+      </c>
+      <c r="AZ17" t="s" s="0">
+        <v>3756</v>
+      </c>
+      <c r="BA17" t="s" s="0">
+        <v>3757</v>
+      </c>
+      <c r="BB17" t="s" s="0">
+        <v>3758</v>
+      </c>
+      <c r="BC17" t="s" s="0">
+        <v>3759</v>
+      </c>
+      <c r="BD17" t="s" s="0">
+        <v>3760</v>
+      </c>
+      <c r="BE17" t="s" s="0">
+        <v>3761</v>
+      </c>
+      <c r="BF17" t="s" s="0">
+        <v>3762</v>
+      </c>
+      <c r="BG17" t="s" s="0">
+        <v>3763</v>
+      </c>
+      <c r="BH17" t="s" s="0">
+        <v>3764</v>
+      </c>
+      <c r="BI17" t="s" s="0">
+        <v>3765</v>
+      </c>
+      <c r="BJ17" t="s" s="0">
+        <v>3766</v>
+      </c>
+      <c r="BK17" t="s" s="0">
+        <v>3767</v>
+      </c>
+      <c r="BL17" t="s" s="0">
+        <v>3768</v>
+      </c>
+      <c r="BM17" t="s" s="0">
+        <v>3769</v>
+      </c>
+      <c r="BN17" t="s" s="0">
+        <v>3770</v>
+      </c>
+      <c r="BO17" t="s" s="0">
+        <v>3771</v>
+      </c>
+      <c r="BP17" t="s" s="0">
+        <v>3772</v>
+      </c>
+      <c r="BQ17" t="s" s="0">
+        <v>3773</v>
+      </c>
+      <c r="BR17" t="s" s="0">
+        <v>3774</v>
+      </c>
+      <c r="BS17" t="s" s="0">
+        <v>3775</v>
+      </c>
+      <c r="BT17" t="s" s="0">
+        <v>3776</v>
+      </c>
+      <c r="BU17" t="s" s="0">
+        <v>3777</v>
+      </c>
+      <c r="BV17" t="s" s="0">
+        <v>3778</v>
+      </c>
+      <c r="BW17" t="s" s="0">
+        <v>3779</v>
+      </c>
+      <c r="BX17" t="s" s="0">
+        <v>3780</v>
+      </c>
+      <c r="BY17" t="s" s="0">
+        <v>3781</v>
+      </c>
+      <c r="BZ17" t="s" s="0">
+        <v>3782</v>
+      </c>
+      <c r="CA17" t="s" s="0">
+        <v>3783</v>
+      </c>
+      <c r="CB17" t="s" s="0">
+        <v>3784</v>
+      </c>
+      <c r="CC17" t="s" s="0">
+        <v>3785</v>
+      </c>
+      <c r="CD17" t="s" s="0">
+        <v>3786</v>
+      </c>
+      <c r="CE17" t="s" s="0">
+        <v>3787</v>
+      </c>
+      <c r="CF17" t="s" s="0">
+        <v>3788</v>
+      </c>
+      <c r="CG17" t="s" s="0">
+        <v>3789</v>
+      </c>
+      <c r="CH17" t="s" s="0">
+        <v>3790</v>
+      </c>
+      <c r="CI17" t="s" s="0">
+        <v>3791</v>
+      </c>
+      <c r="CJ17" t="s" s="0">
+        <v>3792</v>
+      </c>
+      <c r="CK17" t="s" s="0">
+        <v>3793</v>
+      </c>
+      <c r="CL17" t="s" s="0">
+        <v>3794</v>
+      </c>
+      <c r="CM17" t="s" s="0">
+        <v>3795</v>
+      </c>
+      <c r="CN17" t="s" s="0">
+        <v>3796</v>
+      </c>
+      <c r="CO17" t="s" s="0">
+        <v>3797</v>
+      </c>
+      <c r="CP17" t="s" s="0">
+        <v>3798</v>
+      </c>
+      <c r="CQ17" t="s" s="0">
+        <v>3799</v>
+      </c>
+      <c r="CR17" t="s" s="0">
+        <v>3800</v>
+      </c>
+      <c r="CS17" t="s" s="0">
+        <v>3801</v>
+      </c>
+      <c r="CT17" t="s" s="0">
+        <v>3802</v>
+      </c>
+      <c r="CU17" t="s" s="0">
+        <v>3803</v>
+      </c>
+      <c r="CV17" t="s" s="0">
+        <v>3804</v>
+      </c>
+      <c r="CW17" t="s" s="0">
+        <v>3805</v>
+      </c>
+      <c r="CX17" t="s" s="0">
+        <v>3806</v>
+      </c>
+      <c r="CY17" t="s" s="0">
+        <v>3807</v>
+      </c>
+      <c r="CZ17" t="s" s="0">
+        <v>3808</v>
+      </c>
+      <c r="DA17" t="s" s="0">
+        <v>3809</v>
+      </c>
+      <c r="DB17" t="s" s="0">
+        <v>3810</v>
+      </c>
+      <c r="DC17" t="s" s="0">
+        <v>3811</v>
+      </c>
+      <c r="DD17" t="s" s="0">
+        <v>3812</v>
+      </c>
+      <c r="DE17" t="s" s="0">
+        <v>3813</v>
+      </c>
+      <c r="DF17" t="s" s="0">
+        <v>3814</v>
+      </c>
+      <c r="DG17" t="s" s="0">
+        <v>3815</v>
+      </c>
+      <c r="DH17" t="s" s="0">
+        <v>3816</v>
+      </c>
+      <c r="DI17" t="s" s="0">
+        <v>3817</v>
+      </c>
+      <c r="DJ17" t="s" s="0">
+        <v>3818</v>
+      </c>
+      <c r="DK17" t="s" s="0">
+        <v>3819</v>
+      </c>
+      <c r="DL17" t="s" s="0">
+        <v>3820</v>
+      </c>
+      <c r="DM17" t="s" s="0">
+        <v>3821</v>
+      </c>
+      <c r="DN17" t="s" s="0">
+        <v>3822</v>
+      </c>
+      <c r="DO17" t="s" s="0">
+        <v>3823</v>
+      </c>
+      <c r="DP17" t="s" s="0">
+        <v>3824</v>
+      </c>
+      <c r="DQ17" t="s" s="0">
+        <v>3825</v>
+      </c>
+      <c r="DR17" t="s" s="0">
+        <v>3826</v>
+      </c>
+      <c r="DS17" t="s" s="0">
+        <v>3827</v>
+      </c>
+      <c r="DT17" t="s" s="0">
+        <v>3828</v>
+      </c>
+      <c r="DU17" t="s" s="0">
+        <v>3829</v>
+      </c>
+      <c r="DV17" t="s" s="0">
+        <v>3830</v>
+      </c>
+      <c r="DW17" t="s" s="0">
+        <v>3831</v>
+      </c>
+      <c r="DX17" t="s" s="0">
+        <v>3832</v>
+      </c>
+      <c r="DY17" t="s" s="0">
+        <v>3833</v>
+      </c>
+      <c r="DZ17" t="s" s="0">
+        <v>3834</v>
+      </c>
+      <c r="EA17" t="s" s="0">
+        <v>3835</v>
+      </c>
+      <c r="EB17" t="s" s="0">
+        <v>3836</v>
+      </c>
+      <c r="EC17" t="s" s="0">
+        <v>3837</v>
+      </c>
+      <c r="ED17" t="s" s="0">
+        <v>3838</v>
+      </c>
+      <c r="EE17" t="s" s="0">
+        <v>3839</v>
+      </c>
+      <c r="EF17" t="s" s="0">
+        <v>3840</v>
+      </c>
+      <c r="EG17" t="s" s="0">
+        <v>3841</v>
+      </c>
+      <c r="EH17" t="s" s="0">
+        <v>3842</v>
+      </c>
+      <c r="EI17" t="s" s="0">
+        <v>3843</v>
+      </c>
+      <c r="EJ17" t="s" s="0">
+        <v>3844</v>
+      </c>
+      <c r="EK17" t="s" s="0">
+        <v>3845</v>
+      </c>
+      <c r="EL17" t="s" s="0">
+        <v>3846</v>
+      </c>
+      <c r="EM17" t="s" s="0">
+        <v>3847</v>
+      </c>
+      <c r="EN17" t="s" s="0">
+        <v>3848</v>
+      </c>
+      <c r="EO17" t="s" s="0">
+        <v>3849</v>
+      </c>
+      <c r="EP17" t="s" s="0">
+        <v>3850</v>
+      </c>
+      <c r="EQ17" t="s" s="0">
+        <v>3851</v>
+      </c>
+      <c r="ER17" t="s" s="0">
+        <v>3852</v>
+      </c>
+      <c r="ES17" t="s" s="0">
+        <v>3853</v>
+      </c>
+      <c r="ET17" t="s" s="0">
+        <v>3854</v>
+      </c>
+      <c r="EU17" t="s" s="0">
+        <v>3855</v>
+      </c>
+      <c r="EV17" t="s" s="0">
+        <v>3856</v>
+      </c>
+      <c r="EW17" t="s" s="0">
+        <v>3857</v>
+      </c>
+      <c r="EX17" t="s" s="0">
+        <v>3858</v>
+      </c>
+      <c r="EY17" t="s" s="0">
+        <v>3859</v>
+      </c>
+      <c r="EZ17" t="s" s="0">
+        <v>3860</v>
       </c>
     </row>
   </sheetData>
